--- a/KnowledgeSystem/AppResources/317/Templates/TE-701-T001-04 冶金部技術工程師口試報告成績表.xlsx
+++ b/KnowledgeSystem/AppResources/317/Templates/TE-701-T001-04 冶金部技術工程師口試報告成績表.xlsx
@@ -1,23 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\1.經理室\00組務\00歷年文件\6.張氏水\2026年技術工程師評鑑 作業標準修訂\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\01. DEV\01.7System\01.Projects\7system\KnowledgeSystem\AppResources\317\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E478456D-DD6D-4766-BF85-CE78B28AC5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="7245"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -516,11 +529,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="13"/>
       <color theme="1"/>
@@ -675,54 +688,54 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -754,7 +767,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="圖片 2"/>
+        <xdr:cNvPr id="2" name="圖片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1059,12 +1078,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="16.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" style="1" bestFit="1" customWidth="1"/>
@@ -1084,7 +1103,7 @@
     <col min="16" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="21">
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -1097,48 +1116,48 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="O1" s="5"/>
+      <c r="O1" s="18"/>
     </row>
-    <row r="2" spans="1:15" ht="21" x14ac:dyDescent="0.25">
-      <c r="B2" s="12" t="s">
+    <row r="2" spans="1:15" ht="21">
+      <c r="B2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
     </row>
-    <row r="3" spans="1:15" ht="21" x14ac:dyDescent="0.25">
-      <c r="B3" s="12" t="s">
+    <row r="3" spans="1:15" ht="21">
+      <c r="B3" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
     </row>
-    <row r="4" spans="1:15" ht="21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="21">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1152,58 +1171,58 @@
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
     </row>
-    <row r="5" spans="1:15" ht="54.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:15" ht="54.4" customHeight="1">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="6" t="s">
+      <c r="G5" s="17"/>
+      <c r="H5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="7"/>
-      <c r="J5" s="6" t="s">
+      <c r="I5" s="17"/>
+      <c r="J5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="6" t="s">
+      <c r="K5" s="17"/>
+      <c r="L5" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="6" t="s">
+      <c r="M5" s="17"/>
+      <c r="N5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A6" s="9"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="11"/>
+    <row r="6" spans="1:15" ht="38.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="12"/>
       <c r="F6" s="4" t="s">
         <v>19</v>
       </c>
@@ -1228,153 +1247,159 @@
       <c r="M6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="7"/>
-      <c r="O6" s="13"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="15"/>
     </row>
-    <row r="7" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:15" ht="38.25">
+      <c r="A7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="5">
         <v>80</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="5">
         <v>80</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="5">
         <v>80</v>
       </c>
-      <c r="K7" s="17" t="s">
+      <c r="K7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="5">
         <v>78</v>
       </c>
-      <c r="M7" s="17" t="s">
+      <c r="M7" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="5">
         <f>F7*0.4+H7*0.3+J7*0.2+L7*0.1</f>
         <v>79.8</v>
       </c>
-      <c r="O7" s="18">
+      <c r="O7" s="19">
         <f>AVERAGE(N7:N9)</f>
         <v>85.266666666666666</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="19"/>
-      <c r="B8" s="15" t="s">
+    <row r="8" spans="1:15" ht="38.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15" t="s">
+      <c r="C8" s="14"/>
+      <c r="D8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="5">
         <v>86</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="5">
         <v>86</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="5">
         <v>86</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="5">
         <v>86</v>
       </c>
-      <c r="M8" s="17" t="s">
+      <c r="M8" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="5">
         <f t="shared" ref="N8:N9" si="0">F8*0.4+H8*0.3+J8*0.2+L8*0.1</f>
         <v>86</v>
       </c>
-      <c r="O8" s="18">
+      <c r="O8" s="19">
         <v>85.7</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A9" s="9"/>
-      <c r="B9" s="15" t="s">
+    <row r="9" spans="1:15" ht="38.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15" t="s">
+      <c r="C9" s="14"/>
+      <c r="D9" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="5">
         <v>90</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="5">
         <v>90</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="5">
         <v>90</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="K9" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="5">
         <v>90</v>
       </c>
-      <c r="M9" s="17" t="s">
+      <c r="M9" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="5">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="O9" s="18">
+      <c r="O9" s="19">
         <v>85.7</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="17.25">
       <c r="N12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="N5:N6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="E5:E6"/>
@@ -1389,12 +1414,6 @@
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="F5:G5"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="N5:N6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
